--- a/Excels/FlyObject.xlsx
+++ b/Excels/FlyObject.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>id</t>
   </si>
@@ -68,9 +68,6 @@
     <t>箭</t>
   </si>
   <si>
-    <t>arrow</t>
-  </si>
-  <si>
     <t>FlyObject/Arrow</t>
   </si>
   <si>
@@ -79,10 +76,6 @@
   </si>
   <si>
     <t>area</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect/IceArea</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -161,6 +154,26 @@
   </si>
   <si>
     <t>飞行类型(arrow,area,stone,line)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙卷风</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>line</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects/FX_fenglei_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects/冰雪风暴蓝白</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -494,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="3" max="3" width="22.36328125" customWidth="1"/>
@@ -522,13 +535,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" t="s">
         <v>23</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -548,13 +561,13 @@
         <v>6</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -568,19 +581,19 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -591,13 +604,13 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
         <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
       </c>
       <c r="F4" s="3">
         <v>0</v>
@@ -611,22 +624,22 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F5" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -634,22 +647,45 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
       </c>
       <c r="G6">
         <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/FlyObject.xlsx
+++ b/Excels/FlyObject.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9840" windowHeight="3960"/>
+    <workbookView xWindow="-100" yWindow="-360" windowWidth="31570" windowHeight="12380"/>
   </bookViews>
   <sheets>
     <sheet name="FlyObjectCfg" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -133,47 +133,79 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>落地特效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>投石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FlyObject/Store</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙卷风</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>line</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects/FX_fenglei_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects/冰雪风暴蓝白</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jumpArrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全局技能-投石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞行类型(arrow,area,stone,line,jumpArrow,globalStone)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>globalStone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects/FX_火球石头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects/FX_火球石头爆炸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>arrivePrefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>落地特效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>投石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stone</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FlyObject/Store</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>飞行类型(arrow,area,stone,line)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>龙卷风</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>arrow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>line</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effects/FX_fenglei_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effects/冰雪风暴蓝白</t>
+    <t>Effects/FX_飞剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects/FX_飞剑受击</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -507,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="3" max="3" width="22.36328125" customWidth="1"/>
@@ -541,7 +573,7 @@
         <v>18</v>
       </c>
       <c r="H1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -581,7 +613,7 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -593,7 +625,7 @@
         <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -607,7 +639,7 @@
         <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
@@ -633,7 +665,7 @@
         <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F5" s="3">
         <v>0.5</v>
@@ -647,16 +679,16 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6">
         <v>20</v>
       </c>
       <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
         <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
@@ -670,22 +702,74 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F7" s="3">
         <v>0.5</v>
       </c>
       <c r="G7">
         <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>1001</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/FlyObject.xlsx
+++ b/Excels/FlyObject.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
   <si>
     <t>id</t>
   </si>
@@ -181,10 +181,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>飞行类型(arrow,area,stone,line,jumpArrow,globalStone)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>globalStone</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -206,6 +202,73 @@
   </si>
   <si>
     <t>Effects/FX_飞剑受击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乌云后雷电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects/FX_蓝色雷电从天而降爆炸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火箭从天而降爆炸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects/FX_火箭从天而降爆炸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>triggerDamageCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发伤害次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞行类型(arrow,area,areaRandom,stone,line,jumpArrow,globalStone)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>areaRandom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FX_剑落下爆炸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Effects/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FX_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>剑落下爆炸</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -265,7 +328,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -275,6 +338,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -539,18 +603,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="3" max="3" width="22.36328125" customWidth="1"/>
-    <col min="4" max="4" width="56.36328125" customWidth="1"/>
-    <col min="5" max="5" width="29.81640625" customWidth="1"/>
+    <col min="2" max="2" width="22.54296875" customWidth="1"/>
+    <col min="3" max="3" width="29.7265625" customWidth="1"/>
+    <col min="4" max="4" width="67.81640625" customWidth="1"/>
+    <col min="5" max="5" width="35.6328125" customWidth="1"/>
     <col min="6" max="6" width="32.54296875" style="3" customWidth="1"/>
     <col min="7" max="7" width="26.81640625" customWidth="1"/>
-    <col min="8" max="8" width="33" customWidth="1"/>
+    <col min="8" max="9" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -573,10 +638,13 @@
         <v>18</v>
       </c>
       <c r="H1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>38</v>
+      </c>
+      <c r="I1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -601,8 +669,11 @@
       <c r="H2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -613,7 +684,7 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -627,8 +698,11 @@
       <c r="H3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -650,8 +724,11 @@
       <c r="G4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>2</v>
       </c>
@@ -673,8 +750,11 @@
       <c r="G5">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>3</v>
       </c>
@@ -696,8 +776,11 @@
       <c r="G6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>4</v>
       </c>
@@ -719,8 +802,11 @@
       <c r="G7">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>5</v>
       </c>
@@ -734,7 +820,7 @@
         <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
@@ -742,39 +828,123 @@
       <c r="G8">
         <v>10</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9">
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
         <v>1001</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C9">
+      <c r="C12">
         <v>10</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
         <v>36</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>38</v>
+      <c r="I12">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excels/FlyObject.xlsx
+++ b/Excels/FlyObject.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="-360" windowWidth="31570" windowHeight="12380"/>
+    <workbookView xWindow="-100" yWindow="-360" windowWidth="37210" windowHeight="17710"/>
   </bookViews>
   <sheets>
     <sheet name="FlyObjectCfg" sheetId="1" r:id="rId1"/>
@@ -921,7 +921,7 @@
         <v>34</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>

--- a/Excels/FlyObject.xlsx
+++ b/Excels/FlyObject.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="-360" windowWidth="37210" windowHeight="17710"/>
+    <workbookView xWindow="19270" yWindow="9080" windowWidth="19160" windowHeight="9090"/>
   </bookViews>
   <sheets>
     <sheet name="FlyObjectCfg" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
   <si>
     <t>id</t>
   </si>
@@ -69,10 +69,6 @@
   </si>
   <si>
     <t>FlyObject/Arrow</t>
-  </si>
-  <si>
-    <t>冰霜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>area</t>
@@ -149,10 +145,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>龙卷风</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>arrow</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -165,10 +157,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Effects/冰雪风暴蓝白</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>飞剑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -202,10 +190,6 @@
   </si>
   <si>
     <t>Effects/FX_飞剑受击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>乌云后雷电</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -269,6 +253,90 @@
       </rPr>
       <t>剑落下爆炸</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FX_从天而降的拳头土黄色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>area</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects/FX_从天而降的拳头土黄色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FX_红色飓风带雷电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects/FX_红色飓风带雷电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FX_冰箭从天而降爆炸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Effects/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FX_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>冰箭从天而降爆炸</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FX_火焰从天而降</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rea</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects/FX_火焰从天而降</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝色龙卷风</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乌云后雷电</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -603,10 +671,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="22.54296875" customWidth="1"/>
+    <col min="2" max="2" width="41.453125" customWidth="1"/>
     <col min="3" max="3" width="29.7265625" customWidth="1"/>
     <col min="4" max="4" width="67.81640625" customWidth="1"/>
     <col min="5" max="5" width="35.6328125" customWidth="1"/>
@@ -632,16 +700,16 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -661,16 +729,16 @@
         <v>6</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -684,22 +752,22 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -713,7 +781,7 @@
         <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
@@ -732,26 +800,26 @@
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
+      <c r="E5" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="F5" s="3">
         <v>0.5</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -759,16 +827,16 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>20</v>
       </c>
       <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
         <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
@@ -784,17 +852,17 @@
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>27</v>
+      <c r="B7" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="C7">
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F7" s="3">
         <v>0.5</v>
@@ -811,16 +879,16 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
@@ -836,17 +904,17 @@
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" t="s">
-        <v>41</v>
+      <c r="B9" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F9" s="3">
         <v>1</v>
@@ -855,7 +923,7 @@
         <v>5</v>
       </c>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I9">
         <v>5</v>
@@ -866,16 +934,16 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F10" s="3">
         <v>0.5</v>
@@ -892,16 +960,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F11" s="3">
         <v>0</v>
@@ -914,31 +982,109 @@
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="1">
+        <v>11</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="I14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="13" customHeight="1">
+      <c r="A15">
         <v>1001</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15">
+        <v>75</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
         <v>34</v>
       </c>
-      <c r="C12">
-        <v>75</v>
-      </c>
-      <c r="D12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12" t="s">
-        <v>37</v>
-      </c>
-      <c r="I12">
+      <c r="I15">
         <v>-1</v>
       </c>
     </row>

--- a/Excels/FlyObject.xlsx
+++ b/Excels/FlyObject.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyProject\WorldIsMine\Excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="19270" yWindow="9080" windowWidth="19160" windowHeight="9090"/>
+    <workbookView windowHeight="17055"/>
   </bookViews>
   <sheets>
     <sheet name="FlyObjectCfg" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
   <si>
     <t>id</t>
   </si>
@@ -44,46 +49,17 @@
     <t>prefab</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>#备注行</t>
-  </si>
-  <si>
-    <t>名字</t>
-  </si>
-  <si>
-    <t>飞行速度</t>
-  </si>
-  <si>
-    <t>模型名称</t>
-  </si>
-  <si>
-    <t>箭</t>
-  </si>
-  <si>
-    <t>FlyObject/Arrow</t>
-  </si>
-  <si>
-    <t>area</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>伤害间隔（1s)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>damClipTime</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>live</t>
     </r>
     <r>
@@ -91,16 +67,36 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>Time</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arrivePrefab</t>
+  </si>
+  <si>
+    <t>triggerDamageCount</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>float</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>f</t>
     </r>
     <r>
@@ -108,128 +104,63 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>loat</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#备注行</t>
+  </si>
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>飞行速度</t>
+  </si>
+  <si>
+    <t>飞行类型(arrow,area,areaRandom,stone,line,jumpArrow,globalStone,globalArrow,globalLine)</t>
+  </si>
+  <si>
+    <t>模型名称</t>
+  </si>
+  <si>
+    <t>伤害间隔（1s)</t>
   </si>
   <si>
     <t>生命周期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>damClipTime</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>落地特效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>投石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stone</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FlyObject/Store</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发伤害次数</t>
+  </si>
+  <si>
+    <t>箭</t>
   </si>
   <si>
     <t>arrow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>line</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effects/FX_fenglei_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>飞剑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>jumpArrow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全局技能-投石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>globalStone</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effects/FX_火球石头</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effects/FX_火球石头爆炸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>arrivePrefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effects/FX_飞剑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effects/FX_飞剑受击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effects/FX_蓝色雷电从天而降爆炸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火箭从天而降爆炸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effects/FX_火箭从天而降爆炸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>triggerDamageCount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发伤害次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>飞行类型(arrow,area,areaRandom,stone,line,jumpArrow,globalStone)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>areaRandom</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FX_剑落下爆炸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FlyObject/Arrow</t>
+  </si>
+  <si>
+    <t>FX_冰箭从天而降爆炸</t>
+  </si>
+  <si>
+    <t>area</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Effects/</t>
     </r>
     <r>
@@ -237,7 +168,86 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FX_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>冰箭从天而降爆炸</t>
+    </r>
+  </si>
+  <si>
+    <t>投石</t>
+  </si>
+  <si>
+    <t>stone</t>
+  </si>
+  <si>
+    <t>FlyObject/Store</t>
+  </si>
+  <si>
+    <t>蓝色龙卷风</t>
+  </si>
+  <si>
+    <t>line</t>
+  </si>
+  <si>
+    <t>Effects/FX_fenglei_1</t>
+  </si>
+  <si>
+    <t>飞剑</t>
+  </si>
+  <si>
+    <t>jumpArrow</t>
+  </si>
+  <si>
+    <t>Effects/FX_飞剑</t>
+  </si>
+  <si>
+    <t>Effects/FX_飞剑受击</t>
+  </si>
+  <si>
+    <t>乌云后雷电</t>
+  </si>
+  <si>
+    <t>areaRandom</t>
+  </si>
+  <si>
+    <t>Effects/FX_蓝色雷电从天而降爆炸</t>
+  </si>
+  <si>
+    <t>火箭从天而降爆炸</t>
+  </si>
+  <si>
+    <t>Effects/FX_火箭从天而降爆炸</t>
+  </si>
+  <si>
+    <t>FX_剑落下爆炸</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Effects/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -253,46 +263,32 @@
       </rPr>
       <t>剑落下爆炸</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>FX_从天而降的拳头土黄色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>area</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Effects/FX_从天而降的拳头土黄色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>FX_红色飓风带雷电</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Effects/FX_红色飓风带雷电</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FX_冰箭从天而降爆炸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Effects/</t>
-    </r>
+  </si>
+  <si>
+    <t>FX_火焰从天而降</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>FX_</t>
+      <t>a</t>
     </r>
     <r>
       <rPr>
@@ -302,49 +298,54 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>冰箭从天而降爆炸</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FX_火焰从天而降</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>rea</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Effects/FX_火焰从天而降</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蓝色龙卷风</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>乌云后雷电</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全局技能-投石</t>
+  </si>
+  <si>
+    <t>globalStone</t>
+  </si>
+  <si>
+    <t>Effects/FX_火球石头</t>
+  </si>
+  <si>
+    <t>Effects/FX_火球石头爆炸</t>
+  </si>
+  <si>
+    <t>全局技能-漫天箭雨-蓝</t>
+  </si>
+  <si>
+    <t>globalArrow</t>
+  </si>
+  <si>
+    <t>FlyObject/GlobalArrowBlue</t>
+  </si>
+  <si>
+    <t>全局技能-漫天箭雨-红</t>
+  </si>
+  <si>
+    <t>FlyObject/GlobalArrowRed</t>
+  </si>
+  <si>
+    <t>全局技能-火龙吐息</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -353,36 +354,352 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -390,28 +707,318 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -665,21 +1272,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="41.453125" customWidth="1"/>
-    <col min="3" max="3" width="29.7265625" customWidth="1"/>
-    <col min="4" max="4" width="67.81640625" customWidth="1"/>
-    <col min="5" max="5" width="35.6328125" customWidth="1"/>
-    <col min="6" max="6" width="32.54296875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="26.81640625" customWidth="1"/>
+    <col min="2" max="2" width="41.4513274336283" customWidth="1"/>
+    <col min="3" max="3" width="29.7256637168142" customWidth="1"/>
+    <col min="4" max="4" width="67.8141592920354" customWidth="1"/>
+    <col min="5" max="5" width="35.6371681415929" customWidth="1"/>
+    <col min="6" max="6" width="32.5398230088496" style="1" customWidth="1"/>
+    <col min="7" max="7" width="26.8141592920354" customWidth="1"/>
     <col min="8" max="9" width="33" customWidth="1"/>
   </cols>
   <sheetData>
@@ -699,94 +1306,94 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>17</v>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
+      <c r="A2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
+      <c r="A3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I3" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="1">
+      <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="3">
+        <v>24</v>
+      </c>
+      <c r="F4" s="1">
         <v>0</v>
       </c>
       <c r="G4">
@@ -800,19 +1407,19 @@
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>53</v>
+      <c r="B5" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="3">
+        <v>26</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="1">
         <v>0.5</v>
       </c>
       <c r="G5">
@@ -827,18 +1434,18 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="3">
+        <v>30</v>
+      </c>
+      <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6">
@@ -852,19 +1459,19 @@
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>58</v>
+      <c r="B7" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="C7">
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="3">
+        <v>33</v>
+      </c>
+      <c r="F7" s="1">
         <v>0.5</v>
       </c>
       <c r="G7">
@@ -879,52 +1486,53 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8">
         <v>10</v>
       </c>
+      <c r="H8" t="s">
+        <v>37</v>
+      </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>59</v>
+      <c r="B9" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>45</v>
+      <c r="D9" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="3">
+        <v>40</v>
+      </c>
+      <c r="F9" s="1">
         <v>1</v>
       </c>
       <c r="G9">
         <v>5</v>
       </c>
-      <c r="H9" t="s">
-        <v>37</v>
-      </c>
+      <c r="H9"/>
       <c r="I9">
         <v>5</v>
       </c>
@@ -934,18 +1542,18 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="3">
+        <v>42</v>
+      </c>
+      <c r="F10" s="1">
         <v>0.5</v>
       </c>
       <c r="G10">
@@ -956,11 +1564,11 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="1">
+      <c r="A11" s="3">
         <v>8</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -968,62 +1576,62 @@
       <c r="D11" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0</v>
+      <c r="E11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.2</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I11">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="1">
+      <c r="A12" s="3">
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.2</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I12">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="1">
+      <c r="A13" s="3">
         <v>10</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C13">
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" s="3">
+        <v>48</v>
+      </c>
+      <c r="F13" s="1">
         <v>0.5</v>
       </c>
       <c r="G13">
@@ -1034,22 +1642,22 @@
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="1">
+      <c r="A14" s="3">
         <v>11</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>56</v>
+      <c r="D14" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="3">
+        <v>51</v>
+      </c>
+      <c r="F14" s="1">
         <v>0.5</v>
       </c>
       <c r="G14">
@@ -1059,38 +1667,116 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="13" customHeight="1">
+    <row r="15" ht="13" customHeight="1" spans="1:9">
       <c r="A15">
         <v>1001</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C15">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="3">
+        <v>54</v>
+      </c>
+      <c r="F15" s="1">
         <v>0</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
     </row>
+    <row r="16" spans="1:9">
+      <c r="A16">
+        <v>1002</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16">
+        <v>250</v>
+      </c>
+      <c r="D16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="1:9">
+      <c r="A17">
+        <v>1003</v>
+      </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17">
+        <v>250</v>
+      </c>
+      <c r="D17" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="6">
+        <v>1004</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18">
+        <v>100</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G18">
+        <v>10</v>
+      </c>
+      <c r="I18">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Excels/FlyObject.xlsx
+++ b/Excels/FlyObject.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17055"/>
+    <workbookView windowWidth="24140" windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="FlyObjectCfg" sheetId="1" r:id="rId1"/>
@@ -120,7 +120,7 @@
     <t>飞行速度</t>
   </si>
   <si>
-    <t>飞行类型(arrow,area,areaRandom,stone,line,jumpArrow,globalStone,globalArrow,globalLine)</t>
+    <t>飞行类型(arrow,area,areaRandom,stone,line,jumpArrow,globalStone,globalArrow,globalLine,pointToPoint(点对点飞弹))</t>
   </si>
   <si>
     <t>模型名称</t>
@@ -345,14 +345,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -825,147 +818,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1279,14 +1270,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="41.4513274336283" customWidth="1"/>
-    <col min="3" max="3" width="29.7256637168142" customWidth="1"/>
-    <col min="4" max="4" width="67.8141592920354" customWidth="1"/>
-    <col min="5" max="5" width="35.6371681415929" customWidth="1"/>
-    <col min="6" max="6" width="32.5398230088496" style="1" customWidth="1"/>
-    <col min="7" max="7" width="26.8141592920354" customWidth="1"/>
+    <col min="2" max="2" width="41.4545454545455" customWidth="1"/>
+    <col min="3" max="3" width="21.2545454545455" customWidth="1"/>
+    <col min="4" max="4" width="127.127272727273" customWidth="1"/>
+    <col min="5" max="5" width="35.6363636363636" customWidth="1"/>
+    <col min="6" max="6" width="32.5363636363636" style="1" customWidth="1"/>
+    <col min="7" max="7" width="26.8181818181818" customWidth="1"/>
     <col min="8" max="9" width="33" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1532,7 +1523,6 @@
       <c r="G9">
         <v>5</v>
       </c>
-      <c r="H9"/>
       <c r="I9">
         <v>5</v>
       </c>
@@ -1567,7 +1557,7 @@
       <c r="A11" s="3">
         <v>8</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C11">
@@ -1593,7 +1583,7 @@
       <c r="A12" s="3">
         <v>9</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C12">
@@ -1619,7 +1609,7 @@
       <c r="A13" s="3">
         <v>10</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C13">
@@ -1628,7 +1618,7 @@
       <c r="D13" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F13" s="1">
@@ -1645,7 +1635,7 @@
       <c r="A14" s="3">
         <v>11</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C14">
@@ -1654,7 +1644,7 @@
       <c r="D14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F14" s="1">
@@ -1749,10 +1739,10 @@
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6">
+      <c r="A18" s="4">
         <v>1004</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>61</v>
       </c>
       <c r="C18">

--- a/Excels/FlyObject.xlsx
+++ b/Excels/FlyObject.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24140" windowHeight="17680"/>
+    <workbookView windowWidth="29010" windowHeight="12840"/>
   </bookViews>
   <sheets>
     <sheet name="FlyObjectCfg" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="76">
   <si>
     <t>id</t>
   </si>
@@ -80,6 +80,9 @@
     <t>triggerDamageCount</t>
   </si>
   <si>
+    <t>flyParam</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -120,7 +123,7 @@
     <t>飞行速度</t>
   </si>
   <si>
-    <t>飞行类型(arrow,area,areaRandom,stone,line,jumpArrow,globalStone,globalArrow,globalLine,pointToPoint(点对点飞弹))</t>
+    <t>飞行类型(arrow,area,areaRandom,stone,line,jumpArrow,globalStone,globalArrow,globalLine,pointToPoint(点对点飞弹),aroundArea,createWall,blackHall)</t>
   </si>
   <si>
     <t>模型名称</t>
@@ -136,6 +139,9 @@
   </si>
   <si>
     <t>触发伤害次数</t>
+  </si>
+  <si>
+    <t>飞行器参数</t>
   </si>
   <si>
     <t>箭</t>
@@ -305,6 +311,42 @@
     <t>Effects/FX_火焰从天而降</t>
   </si>
   <si>
+    <t>FX</t>
+  </si>
+  <si>
+    <t>aroundArea</t>
+  </si>
+  <si>
+    <t>Effects/FX</t>
+  </si>
+  <si>
+    <t>FX_长驱直入</t>
+  </si>
+  <si>
+    <t>FX_wall</t>
+  </si>
+  <si>
+    <t>createWall</t>
+  </si>
+  <si>
+    <t>FX_ball</t>
+  </si>
+  <si>
+    <t>pointToPoint</t>
+  </si>
+  <si>
+    <t>3,0.1</t>
+  </si>
+  <si>
+    <t>FX_blackHall</t>
+  </si>
+  <si>
+    <t>blackHall</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>全局技能-投石</t>
   </si>
   <si>
@@ -332,7 +374,7 @@
     <t>FlyObject/GlobalArrowRed</t>
   </si>
   <si>
-    <t>全局技能-火龙吐息</t>
+    <t>全局技能-火烧连营</t>
   </si>
 </sst>
 </file>
@@ -948,11 +990,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1269,19 +1314,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="41.4545454545455" customWidth="1"/>
     <col min="3" max="3" width="21.2545454545455" customWidth="1"/>
-    <col min="4" max="4" width="127.127272727273" customWidth="1"/>
+    <col min="4" max="4" width="144.490909090909" customWidth="1"/>
     <col min="5" max="5" width="35.6363636363636" customWidth="1"/>
     <col min="6" max="6" width="32.5363636363636" style="1" customWidth="1"/>
     <col min="7" max="7" width="26.8181818181818" customWidth="1"/>
     <col min="8" max="9" width="33" customWidth="1"/>
+    <col min="10" max="10" width="15.4" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1300,7 +1346,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
@@ -1309,80 +1355,89 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>15</v>
       </c>
+      <c r="C3" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="G3" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="3">
+        <v>22</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="4">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>22</v>
+      <c r="B4" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1394,21 +1449,21 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>25</v>
+      <c r="B5" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F5" s="1">
         <v>0.5</v>
@@ -1420,21 +1475,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -1446,21 +1501,21 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>31</v>
+      <c r="B7" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="C7">
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F7" s="1">
         <v>0.5</v>
@@ -1472,21 +1527,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8">
         <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1495,27 +1550,27 @@
         <v>10</v>
       </c>
       <c r="H8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I8">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>38</v>
+      <c r="B9" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>39</v>
+      <c r="D9" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
@@ -1527,21 +1582,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F10" s="1">
         <v>0.5</v>
@@ -1553,21 +1608,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="3">
+    <row r="11" spans="1:10">
+      <c r="A11" s="4">
         <v>8</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>43</v>
+      <c r="B11" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>44</v>
+        <v>28</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="F11" s="1">
         <v>0.2</v>
@@ -1579,21 +1634,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="3">
+    <row r="12" spans="1:10">
+      <c r="A12" s="4">
         <v>9</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>45</v>
+      <c r="B12" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>46</v>
+        <v>28</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="F12" s="1">
         <v>0.2</v>
@@ -1605,21 +1660,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="3">
+    <row r="13" spans="1:10">
+      <c r="A13" s="4">
         <v>10</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>47</v>
+      <c r="B13" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="C13">
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>48</v>
+        <v>34</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="F13" s="1">
         <v>0.5</v>
@@ -1631,21 +1686,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="3">
+    <row r="14" spans="1:10">
+      <c r="A14" s="4">
         <v>11</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>49</v>
+      <c r="B14" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>51</v>
+      <c r="D14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="F14" s="1">
         <v>0.5</v>
@@ -1657,110 +1712,250 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" ht="13" customHeight="1" spans="1:9">
-      <c r="A15">
-        <v>1001</v>
-      </c>
-      <c r="B15" t="s">
-        <v>52</v>
+    <row r="15" customFormat="1" spans="1:10">
+      <c r="A15" s="4">
+        <v>12</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="C15">
-        <v>80</v>
-      </c>
-      <c r="D15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" t="s">
-        <v>54</v>
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15" t="s">
+        <v>5</v>
+      </c>
+      <c r="I15">
+        <v>10</v>
+      </c>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" customFormat="1" spans="1:10">
+      <c r="A16" s="4">
+        <v>13</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16">
-        <v>1002</v>
-      </c>
-      <c r="B16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16">
-        <v>250</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="E16" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E16" t="s">
-        <v>58</v>
-      </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>-1</v>
       </c>
-    </row>
-    <row r="17" customFormat="1" spans="1:9">
-      <c r="A17">
-        <v>1003</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" customFormat="1" spans="1:10">
+      <c r="A17" s="4">
+        <v>14</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C17">
-        <v>250</v>
-      </c>
-      <c r="D17" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" t="s">
-        <v>60</v>
+      <c r="E17" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I17">
         <v>-1</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" customFormat="1" spans="1:10">
       <c r="A18" s="4">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>-1</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="1:10">
+      <c r="A19" s="4">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="I19">
+        <v>-1</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" ht="13" customHeight="1" spans="1:10">
+      <c r="A20">
+        <v>1001</v>
+      </c>
+      <c r="B20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20">
+        <v>80</v>
+      </c>
+      <c r="D20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21">
+        <v>1002</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21">
+        <v>250</v>
+      </c>
+      <c r="D21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:10">
+      <c r="A22">
+        <v>1003</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22">
+        <v>250</v>
+      </c>
+      <c r="D22" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>-1</v>
+      </c>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="5">
         <v>1004</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18">
+      <c r="B23" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23">
         <v>100</v>
       </c>
-      <c r="D18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" s="1">
+      <c r="D23" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="1">
         <v>0.5</v>
       </c>
-      <c r="G18">
+      <c r="G23">
         <v>10</v>
       </c>
-      <c r="I18">
+      <c r="I23">
         <v>50</v>
       </c>
     </row>

--- a/Excels/FlyObject.xlsx
+++ b/Excels/FlyObject.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="77">
   <si>
     <t>id</t>
   </si>
@@ -123,7 +123,7 @@
     <t>飞行速度</t>
   </si>
   <si>
-    <t>飞行类型(arrow,area,areaRandom,stone,line,jumpArrow,globalStone,globalArrow,globalLine,pointToPoint(点对点飞弹),aroundArea,createWall,blackHall)</t>
+    <t>飞行类型(arrow,area,areaRandom,stone,line,jumpArrow,globalStone,globalArrow,globalLine,pointToPoint(点对点飞弹),aroundArea,createWall,blackHall,translateArea)</t>
   </si>
   <si>
     <t>模型名称</t>
@@ -311,15 +311,12 @@
     <t>Effects/FX_火焰从天而降</t>
   </si>
   <si>
-    <t>FX</t>
+    <t>FX_周围攻击效果</t>
   </si>
   <si>
     <t>aroundArea</t>
   </si>
   <si>
-    <t>Effects/FX</t>
-  </si>
-  <si>
     <t>FX_长驱直入</t>
   </si>
   <si>
@@ -345,6 +342,12 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>FX_translateArea</t>
+  </si>
+  <si>
+    <t>translateArea</t>
   </si>
   <si>
     <t>全局技能-投石</t>
@@ -1314,12 +1317,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="41.4545454545455" customWidth="1"/>
     <col min="3" max="3" width="21.2545454545455" customWidth="1"/>
-    <col min="4" max="4" width="144.490909090909" customWidth="1"/>
+    <col min="4" max="4" width="167.490909090909" customWidth="1"/>
     <col min="5" max="5" width="35.6363636363636" customWidth="1"/>
     <col min="6" max="6" width="32.5363636363636" style="1" customWidth="1"/>
     <col min="7" max="7" width="26.8181818181818" customWidth="1"/>
@@ -1726,7 +1729,7 @@
         <v>55</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F15" s="1">
         <v>0.5</v>
@@ -1744,7 +1747,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1753,7 +1756,7 @@
         <v>55</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F16" s="1">
         <v>0.1</v>
@@ -1771,16 +1774,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="E17" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1798,16 +1801,16 @@
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18">
+        <v>80</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="E18" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1819,7 +1822,7 @@
         <v>-1</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" customFormat="1" spans="1:10">
@@ -1827,16 +1830,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>64</v>
-      </c>
       <c r="E19" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -1848,79 +1851,80 @@
         <v>-1</v>
       </c>
       <c r="J19" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="1:10">
+      <c r="A20" s="4">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="20" ht="13" customHeight="1" spans="1:10">
-      <c r="A20">
-        <v>1001</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C20">
-        <v>80</v>
-      </c>
-      <c r="D20" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" t="s">
-        <v>68</v>
+      <c r="E20" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" ht="13" customHeight="1" spans="1:10">
       <c r="A21">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21">
+        <v>80</v>
+      </c>
+      <c r="D21" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
         <v>70</v>
-      </c>
-      <c r="C21">
-        <v>250</v>
-      </c>
-      <c r="D21" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" t="s">
-        <v>72</v>
-      </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
     </row>
-    <row r="22" customFormat="1" spans="1:10">
+    <row r="22" spans="1:10">
       <c r="A22">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C22">
         <v>250</v>
       </c>
       <c r="D22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -1931,31 +1935,57 @@
       <c r="I22">
         <v>-1</v>
       </c>
-      <c r="J22" s="2"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="5">
+    </row>
+    <row r="23" customFormat="1" spans="1:10">
+      <c r="A23">
+        <v>1003</v>
+      </c>
+      <c r="B23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23">
+        <v>250</v>
+      </c>
+      <c r="D23" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>-1</v>
+      </c>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="5">
         <v>1004</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B24" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24">
+        <v>100</v>
+      </c>
+      <c r="D24" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" t="s">
         <v>75</v>
       </c>
-      <c r="C23">
-        <v>100</v>
-      </c>
-      <c r="D23" t="s">
-        <v>34</v>
-      </c>
-      <c r="E23" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="1">
+      <c r="F24" s="1">
         <v>0.5</v>
       </c>
-      <c r="G23">
+      <c r="G24">
         <v>10</v>
       </c>
-      <c r="I23">
+      <c r="I24">
         <v>50</v>
       </c>
     </row>
